--- a/datasets/MLK/MatchupTable.xlsx
+++ b/datasets/MLK/MatchupTable.xlsx
@@ -2813,7 +2813,7 @@
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="C54" s="1" t="n">
@@ -2875,7 +2875,7 @@
       <c r="A55" s="1" t="n"/>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="C55" s="1" t="n">
@@ -2917,7 +2917,7 @@
       <c r="A56" s="1" t="n"/>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="C56" s="1" t="n">
@@ -2959,7 +2959,7 @@
       <c r="A57" s="1" t="n"/>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="C57" s="1" t="n">
@@ -3337,7 +3337,7 @@
       <c r="A66" s="1" t="n"/>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>269.3</t>
+          <t>269.21</t>
         </is>
       </c>
       <c r="C66" s="1" t="n">
@@ -3379,7 +3379,7 @@
       <c r="A67" s="1" t="n"/>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>269.3</t>
+          <t>269.21</t>
         </is>
       </c>
       <c r="C67" s="1" t="n">
@@ -3421,7 +3421,7 @@
       <c r="A68" s="1" t="n"/>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>269.3</t>
+          <t>269.21</t>
         </is>
       </c>
       <c r="C68" s="1" t="n">
@@ -3463,7 +3463,7 @@
       <c r="A69" s="1" t="n"/>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>269.3</t>
+          <t>269.21</t>
         </is>
       </c>
       <c r="C69" s="1" t="n">
@@ -10241,20 +10241,14 @@
           <t>7</t>
         </is>
       </c>
-      <c r="H231" s="1" t="inlineStr">
-        <is>
-          <t>10292024</t>
-        </is>
-      </c>
-      <c r="I231" s="1" t="inlineStr">
-        <is>
-          <t>MLK Blvd and Houston St</t>
-        </is>
-      </c>
-      <c r="J231" s="1" t="inlineStr">
-        <is>
-          <t>NBR</t>
-        </is>
+      <c r="H231" s="1" t="n">
+        <v/>
+      </c>
+      <c r="I231" s="1" t="n">
+        <v/>
+      </c>
+      <c r="J231" s="1" t="n">
+        <v/>
       </c>
       <c r="K231" s="1" t="n"/>
       <c r="L231" s="1" t="inlineStr">
@@ -10269,7 +10263,7 @@
       </c>
       <c r="N231" s="1" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -10301,10 +10295,8 @@
       <c r="G232" s="1" t="n"/>
       <c r="H232" s="1" t="n"/>
       <c r="I232" s="1" t="n"/>
-      <c r="J232" s="1" t="inlineStr">
-        <is>
-          <t>NBT</t>
-        </is>
+      <c r="J232" s="1" t="n">
+        <v/>
       </c>
       <c r="K232" s="1" t="n"/>
       <c r="L232" s="1" t="n"/>
@@ -10343,10 +10335,8 @@
       <c r="G233" s="1" t="n"/>
       <c r="H233" s="1" t="n"/>
       <c r="I233" s="1" t="n"/>
-      <c r="J233" s="1" t="inlineStr">
-        <is>
-          <t>NBL</t>
-        </is>
+      <c r="J233" s="1" t="n">
+        <v/>
       </c>
       <c r="K233" s="1" t="n"/>
       <c r="L233" s="1" t="n"/>
@@ -10385,10 +10375,8 @@
       <c r="G234" s="1" t="n"/>
       <c r="H234" s="1" t="n"/>
       <c r="I234" s="1" t="n"/>
-      <c r="J234" s="1" t="inlineStr">
-        <is>
-          <t>NBU</t>
-        </is>
+      <c r="J234" s="1" t="n">
+        <v/>
       </c>
       <c r="K234" s="1" t="n"/>
       <c r="L234" s="1" t="n"/>
@@ -10427,10 +10415,8 @@
       <c r="G235" s="1" t="n"/>
       <c r="H235" s="1" t="n"/>
       <c r="I235" s="1" t="n"/>
-      <c r="J235" s="1" t="inlineStr">
-        <is>
-          <t>EBR</t>
-        </is>
+      <c r="J235" s="1" t="n">
+        <v/>
       </c>
       <c r="K235" s="1" t="n"/>
       <c r="L235" s="1" t="n"/>
@@ -10469,10 +10455,8 @@
       <c r="G236" s="1" t="n"/>
       <c r="H236" s="1" t="n"/>
       <c r="I236" s="1" t="n"/>
-      <c r="J236" s="1" t="inlineStr">
-        <is>
-          <t>EBT</t>
-        </is>
+      <c r="J236" s="1" t="n">
+        <v/>
       </c>
       <c r="K236" s="1" t="n"/>
       <c r="L236" s="1" t="n"/>
@@ -10511,10 +10495,8 @@
       <c r="G237" s="1" t="n"/>
       <c r="H237" s="1" t="n"/>
       <c r="I237" s="1" t="n"/>
-      <c r="J237" s="1" t="inlineStr">
-        <is>
-          <t>EBL</t>
-        </is>
+      <c r="J237" s="1" t="n">
+        <v/>
       </c>
       <c r="K237" s="1" t="n"/>
       <c r="L237" s="1" t="n"/>
@@ -10553,10 +10535,8 @@
       <c r="G238" s="1" t="n"/>
       <c r="H238" s="1" t="n"/>
       <c r="I238" s="1" t="n"/>
-      <c r="J238" s="1" t="inlineStr">
-        <is>
-          <t>EBU</t>
-        </is>
+      <c r="J238" s="1" t="n">
+        <v/>
       </c>
       <c r="K238" s="1" t="n"/>
       <c r="L238" s="1" t="n"/>
@@ -10595,10 +10575,8 @@
       <c r="G239" s="1" t="n"/>
       <c r="H239" s="1" t="n"/>
       <c r="I239" s="1" t="n"/>
-      <c r="J239" s="1" t="inlineStr">
-        <is>
-          <t>SBR</t>
-        </is>
+      <c r="J239" s="1" t="n">
+        <v/>
       </c>
       <c r="K239" s="1" t="n"/>
       <c r="L239" s="1" t="n"/>
@@ -10637,10 +10615,8 @@
       <c r="G240" s="1" t="n"/>
       <c r="H240" s="1" t="n"/>
       <c r="I240" s="1" t="n"/>
-      <c r="J240" s="1" t="inlineStr">
-        <is>
-          <t>SBT</t>
-        </is>
+      <c r="J240" s="1" t="n">
+        <v/>
       </c>
       <c r="K240" s="1" t="n"/>
       <c r="L240" s="1" t="n"/>
@@ -10679,10 +10655,8 @@
       <c r="G241" s="1" t="n"/>
       <c r="H241" s="1" t="n"/>
       <c r="I241" s="1" t="n"/>
-      <c r="J241" s="1" t="inlineStr">
-        <is>
-          <t>SBL</t>
-        </is>
+      <c r="J241" s="1" t="n">
+        <v/>
       </c>
       <c r="K241" s="1" t="n"/>
       <c r="L241" s="1" t="n"/>
@@ -10721,10 +10695,8 @@
       <c r="G242" s="1" t="n"/>
       <c r="H242" s="1" t="n"/>
       <c r="I242" s="1" t="n"/>
-      <c r="J242" s="1" t="inlineStr">
-        <is>
-          <t>SBU</t>
-        </is>
+      <c r="J242" s="1" t="n">
+        <v/>
       </c>
       <c r="K242" s="1" t="n"/>
       <c r="L242" s="1" t="n"/>
@@ -10763,10 +10735,8 @@
       <c r="G243" s="1" t="n"/>
       <c r="H243" s="1" t="n"/>
       <c r="I243" s="1" t="n"/>
-      <c r="J243" s="1" t="inlineStr">
-        <is>
-          <t>WBR</t>
-        </is>
+      <c r="J243" s="1" t="n">
+        <v/>
       </c>
       <c r="K243" s="1" t="n"/>
       <c r="L243" s="1" t="n"/>
@@ -10805,10 +10775,8 @@
       <c r="G244" s="1" t="n"/>
       <c r="H244" s="1" t="n"/>
       <c r="I244" s="1" t="n"/>
-      <c r="J244" s="1" t="inlineStr">
-        <is>
-          <t>WBT</t>
-        </is>
+      <c r="J244" s="1" t="n">
+        <v/>
       </c>
       <c r="K244" s="1" t="n"/>
       <c r="L244" s="1" t="n"/>
@@ -10847,10 +10815,8 @@
       <c r="G245" s="1" t="n"/>
       <c r="H245" s="1" t="n"/>
       <c r="I245" s="1" t="n"/>
-      <c r="J245" s="1" t="inlineStr">
-        <is>
-          <t>WBL</t>
-        </is>
+      <c r="J245" s="1" t="n">
+        <v/>
       </c>
       <c r="K245" s="1" t="n"/>
       <c r="L245" s="1" t="n"/>
@@ -10889,10 +10855,8 @@
       <c r="G246" s="1" t="n"/>
       <c r="H246" s="1" t="n"/>
       <c r="I246" s="1" t="n"/>
-      <c r="J246" s="1" t="inlineStr">
-        <is>
-          <t>WBU</t>
-        </is>
+      <c r="J246" s="1" t="n">
+        <v/>
       </c>
       <c r="K246" s="1" t="n"/>
       <c r="L246" s="1" t="n"/>
